--- a/outputs/192-22.xlsx
+++ b/outputs/192-22.xlsx
@@ -678,52 +678,56 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -981,1592 +985,1592 @@
   <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D2)))&gt;0,"Billing PO","")</f>
+      <c r="F2" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D2)),ISNUMBER(SEARCH("Core Design",D2)),ISNUMBER(SEARCH("Mobile Terminology",D2)),ISNUMBER(SEARCH("Mobile Design",D2)),ISNUMBER(SEARCH("Mobile Integration",D2)),ISNUMBER(SEARCH("Testing Layer",D2)),ISNUMBER(SEARCH("Testing Offshore",D2)),ISNUMBER(SEARCH("Carrier",D2)),ISNUMBER(SEARCH("Barrier",D2))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D3)))&gt;0,"Billing PO","")</f>
+      <c r="F3" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D3)),ISNUMBER(SEARCH("Core Design",D3)),ISNUMBER(SEARCH("Mobile Terminology",D3)),ISNUMBER(SEARCH("Mobile Design",D3)),ISNUMBER(SEARCH("Mobile Integration",D3)),ISNUMBER(SEARCH("Testing Layer",D3)),ISNUMBER(SEARCH("Testing Offshore",D3)),ISNUMBER(SEARCH("Carrier",D3)),ISNUMBER(SEARCH("Barrier",D3))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D4)))&gt;0,"Billing PO","")</f>
+      <c r="F4" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D4)),ISNUMBER(SEARCH("Core Design",D4)),ISNUMBER(SEARCH("Mobile Terminology",D4)),ISNUMBER(SEARCH("Mobile Design",D4)),ISNUMBER(SEARCH("Mobile Integration",D4)),ISNUMBER(SEARCH("Testing Layer",D4)),ISNUMBER(SEARCH("Testing Offshore",D4)),ISNUMBER(SEARCH("Carrier",D4)),ISNUMBER(SEARCH("Barrier",D4))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D5)))&gt;0,"Billing PO","")</f>
+      <c r="F5" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D5)),ISNUMBER(SEARCH("Core Design",D5)),ISNUMBER(SEARCH("Mobile Terminology",D5)),ISNUMBER(SEARCH("Mobile Design",D5)),ISNUMBER(SEARCH("Mobile Integration",D5)),ISNUMBER(SEARCH("Testing Layer",D5)),ISNUMBER(SEARCH("Testing Offshore",D5)),ISNUMBER(SEARCH("Carrier",D5)),ISNUMBER(SEARCH("Barrier",D5))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D6)))&gt;0,"Billing PO","")</f>
+      <c r="F6" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D6)),ISNUMBER(SEARCH("Core Design",D6)),ISNUMBER(SEARCH("Mobile Terminology",D6)),ISNUMBER(SEARCH("Mobile Design",D6)),ISNUMBER(SEARCH("Mobile Integration",D6)),ISNUMBER(SEARCH("Testing Layer",D6)),ISNUMBER(SEARCH("Testing Offshore",D6)),ISNUMBER(SEARCH("Carrier",D6)),ISNUMBER(SEARCH("Barrier",D6))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D7)))&gt;0,"Billing PO","")</f>
-        <v/>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="F7" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D7)),ISNUMBER(SEARCH("Core Design",D7)),ISNUMBER(SEARCH("Mobile Terminology",D7)),ISNUMBER(SEARCH("Mobile Design",D7)),ISNUMBER(SEARCH("Mobile Integration",D7)),ISNUMBER(SEARCH("Testing Layer",D7)),ISNUMBER(SEARCH("Testing Offshore",D7)),ISNUMBER(SEARCH("Carrier",D7)),ISNUMBER(SEARCH("Barrier",D7))),"Billing PO","")</f>
+        <v/>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="B8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D8)))&gt;0,"Billing PO","")</f>
+      <c r="F8" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D8)),ISNUMBER(SEARCH("Core Design",D8)),ISNUMBER(SEARCH("Mobile Terminology",D8)),ISNUMBER(SEARCH("Mobile Design",D8)),ISNUMBER(SEARCH("Mobile Integration",D8)),ISNUMBER(SEARCH("Testing Layer",D8)),ISNUMBER(SEARCH("Testing Offshore",D8)),ISNUMBER(SEARCH("Carrier",D8)),ISNUMBER(SEARCH("Barrier",D8))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="0" t="str">
+      <c r="E9" s="1" t="str">
         <f aca="false">E2</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F9" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D9)))&gt;0,"Billing PO","")</f>
-        <v/>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="F9" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D9)),ISNUMBER(SEARCH("Core Design",D9)),ISNUMBER(SEARCH("Mobile Terminology",D9)),ISNUMBER(SEARCH("Mobile Design",D9)),ISNUMBER(SEARCH("Mobile Integration",D9)),ISNUMBER(SEARCH("Testing Layer",D9)),ISNUMBER(SEARCH("Testing Offshore",D9)),ISNUMBER(SEARCH("Carrier",D9)),ISNUMBER(SEARCH("Barrier",D9))),"Billing PO","")</f>
+        <v/>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="0" t="str">
+      <c r="E10" s="1" t="str">
         <f aca="false">E3</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F10" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D10)))&gt;0,"Billing PO","")</f>
-        <v/>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="F10" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D10)),ISNUMBER(SEARCH("Core Design",D10)),ISNUMBER(SEARCH("Mobile Terminology",D10)),ISNUMBER(SEARCH("Mobile Design",D10)),ISNUMBER(SEARCH("Mobile Integration",D10)),ISNUMBER(SEARCH("Testing Layer",D10)),ISNUMBER(SEARCH("Testing Offshore",D10)),ISNUMBER(SEARCH("Carrier",D10)),ISNUMBER(SEARCH("Barrier",D10))),"Billing PO","")</f>
+        <v/>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="0" t="str">
+      <c r="E11" s="1" t="str">
         <f aca="false">E4</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F11" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D11)))&gt;0,"Billing PO","")</f>
-        <v/>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="F11" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D11)),ISNUMBER(SEARCH("Core Design",D11)),ISNUMBER(SEARCH("Mobile Terminology",D11)),ISNUMBER(SEARCH("Mobile Design",D11)),ISNUMBER(SEARCH("Mobile Integration",D11)),ISNUMBER(SEARCH("Testing Layer",D11)),ISNUMBER(SEARCH("Testing Offshore",D11)),ISNUMBER(SEARCH("Carrier",D11)),ISNUMBER(SEARCH("Barrier",D11))),"Billing PO","")</f>
+        <v/>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="B12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="0" t="str">
+      <c r="E12" s="1" t="str">
         <f aca="false">E5</f>
         <v> SNMP</v>
       </c>
-      <c r="F12" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D12)))&gt;0,"Billing PO","")</f>
-        <v/>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="F12" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D12)),ISNUMBER(SEARCH("Core Design",D12)),ISNUMBER(SEARCH("Mobile Terminology",D12)),ISNUMBER(SEARCH("Mobile Design",D12)),ISNUMBER(SEARCH("Mobile Integration",D12)),ISNUMBER(SEARCH("Testing Layer",D12)),ISNUMBER(SEARCH("Testing Offshore",D12)),ISNUMBER(SEARCH("Carrier",D12)),ISNUMBER(SEARCH("Barrier",D12))),"Billing PO","")</f>
+        <v/>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="0" t="str">
+      <c r="E13" s="1" t="str">
         <f aca="false">E6</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F13" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D13)))&gt;0,"Billing PO","")</f>
+      <c r="F13" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D13)),ISNUMBER(SEARCH("Core Design",D13)),ISNUMBER(SEARCH("Mobile Terminology",D13)),ISNUMBER(SEARCH("Mobile Design",D13)),ISNUMBER(SEARCH("Mobile Integration",D13)),ISNUMBER(SEARCH("Testing Layer",D13)),ISNUMBER(SEARCH("Testing Offshore",D13)),ISNUMBER(SEARCH("Carrier",D13)),ISNUMBER(SEARCH("Barrier",D13))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="B14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="0" t="str">
+      <c r="E14" s="1" t="str">
         <f aca="false">E7</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F14" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D14)))&gt;0,"Billing PO","")</f>
+      <c r="F14" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D14)),ISNUMBER(SEARCH("Core Design",D14)),ISNUMBER(SEARCH("Mobile Terminology",D14)),ISNUMBER(SEARCH("Mobile Design",D14)),ISNUMBER(SEARCH("Mobile Integration",D14)),ISNUMBER(SEARCH("Testing Layer",D14)),ISNUMBER(SEARCH("Testing Offshore",D14)),ISNUMBER(SEARCH("Carrier",D14)),ISNUMBER(SEARCH("Barrier",D14))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="0" t="str">
+      <c r="E15" s="1" t="str">
         <f aca="false">E8</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F15" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D15)))&gt;0,"Billing PO","")</f>
+      <c r="F15" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D15)),ISNUMBER(SEARCH("Core Design",D15)),ISNUMBER(SEARCH("Mobile Terminology",D15)),ISNUMBER(SEARCH("Mobile Design",D15)),ISNUMBER(SEARCH("Mobile Integration",D15)),ISNUMBER(SEARCH("Testing Layer",D15)),ISNUMBER(SEARCH("Testing Offshore",D15)),ISNUMBER(SEARCH("Carrier",D15)),ISNUMBER(SEARCH("Barrier",D15))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="B16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="0" t="str">
+      <c r="E16" s="1" t="str">
         <f aca="false">E9</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F16" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D16)))&gt;0,"Billing PO","")</f>
+      <c r="F16" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D16)),ISNUMBER(SEARCH("Core Design",D16)),ISNUMBER(SEARCH("Mobile Terminology",D16)),ISNUMBER(SEARCH("Mobile Design",D16)),ISNUMBER(SEARCH("Mobile Integration",D16)),ISNUMBER(SEARCH("Testing Layer",D16)),ISNUMBER(SEARCH("Testing Offshore",D16)),ISNUMBER(SEARCH("Carrier",D16)),ISNUMBER(SEARCH("Barrier",D16))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="0" t="str">
+      <c r="E17" s="1" t="str">
         <f aca="false">E10</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F17" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D17)))&gt;0,"Billing PO","")</f>
+      <c r="F17" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D17)),ISNUMBER(SEARCH("Core Design",D17)),ISNUMBER(SEARCH("Mobile Terminology",D17)),ISNUMBER(SEARCH("Mobile Design",D17)),ISNUMBER(SEARCH("Mobile Integration",D17)),ISNUMBER(SEARCH("Testing Layer",D17)),ISNUMBER(SEARCH("Testing Offshore",D17)),ISNUMBER(SEARCH("Carrier",D17)),ISNUMBER(SEARCH("Barrier",D17))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="B18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="0" t="str">
+      <c r="E18" s="1" t="str">
         <f aca="false">E11</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F18" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D18)))&gt;0,"Billing PO","")</f>
+      <c r="F18" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D18)),ISNUMBER(SEARCH("Core Design",D18)),ISNUMBER(SEARCH("Mobile Terminology",D18)),ISNUMBER(SEARCH("Mobile Design",D18)),ISNUMBER(SEARCH("Mobile Integration",D18)),ISNUMBER(SEARCH("Testing Layer",D18)),ISNUMBER(SEARCH("Testing Offshore",D18)),ISNUMBER(SEARCH("Carrier",D18)),ISNUMBER(SEARCH("Barrier",D18))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="0" t="str">
+      <c r="E19" s="1" t="str">
         <f aca="false">E12</f>
         <v> SNMP</v>
       </c>
-      <c r="F19" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D19)))&gt;0,"Billing PO","")</f>
+      <c r="F19" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D19)),ISNUMBER(SEARCH("Core Design",D19)),ISNUMBER(SEARCH("Mobile Terminology",D19)),ISNUMBER(SEARCH("Mobile Design",D19)),ISNUMBER(SEARCH("Mobile Integration",D19)),ISNUMBER(SEARCH("Testing Layer",D19)),ISNUMBER(SEARCH("Testing Offshore",D19)),ISNUMBER(SEARCH("Carrier",D19)),ISNUMBER(SEARCH("Barrier",D19))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="0" t="str">
+      <c r="E20" s="1" t="str">
         <f aca="false">E13</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F20" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D20)))&gt;0,"Billing PO","")</f>
+      <c r="F20" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D20)),ISNUMBER(SEARCH("Core Design",D20)),ISNUMBER(SEARCH("Mobile Terminology",D20)),ISNUMBER(SEARCH("Mobile Design",D20)),ISNUMBER(SEARCH("Mobile Integration",D20)),ISNUMBER(SEARCH("Testing Layer",D20)),ISNUMBER(SEARCH("Testing Offshore",D20)),ISNUMBER(SEARCH("Carrier",D20)),ISNUMBER(SEARCH("Barrier",D20))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="0" t="str">
+      <c r="E21" s="1" t="str">
         <f aca="false">E14</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F21" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D21)))&gt;0,"Billing PO","")</f>
+      <c r="F21" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D21)),ISNUMBER(SEARCH("Core Design",D21)),ISNUMBER(SEARCH("Mobile Terminology",D21)),ISNUMBER(SEARCH("Mobile Design",D21)),ISNUMBER(SEARCH("Mobile Integration",D21)),ISNUMBER(SEARCH("Testing Layer",D21)),ISNUMBER(SEARCH("Testing Offshore",D21)),ISNUMBER(SEARCH("Carrier",D21)),ISNUMBER(SEARCH("Barrier",D21))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="B22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="0" t="str">
+      <c r="E22" s="1" t="str">
         <f aca="false">E15</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F22" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D22)))&gt;0,"Billing PO","")</f>
+      <c r="F22" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D22)),ISNUMBER(SEARCH("Core Design",D22)),ISNUMBER(SEARCH("Mobile Terminology",D22)),ISNUMBER(SEARCH("Mobile Design",D22)),ISNUMBER(SEARCH("Mobile Integration",D22)),ISNUMBER(SEARCH("Testing Layer",D22)),ISNUMBER(SEARCH("Testing Offshore",D22)),ISNUMBER(SEARCH("Carrier",D22)),ISNUMBER(SEARCH("Barrier",D22))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="0" t="str">
+      <c r="E23" s="1" t="str">
         <f aca="false">E16</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F23" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D23)))&gt;0,"Billing PO","")</f>
+      <c r="F23" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D23)),ISNUMBER(SEARCH("Core Design",D23)),ISNUMBER(SEARCH("Mobile Terminology",D23)),ISNUMBER(SEARCH("Mobile Design",D23)),ISNUMBER(SEARCH("Mobile Integration",D23)),ISNUMBER(SEARCH("Testing Layer",D23)),ISNUMBER(SEARCH("Testing Offshore",D23)),ISNUMBER(SEARCH("Carrier",D23)),ISNUMBER(SEARCH("Barrier",D23))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="B24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="0" t="str">
+      <c r="E24" s="1" t="str">
         <f aca="false">E17</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F24" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D24)))&gt;0,"Billing PO","")</f>
+      <c r="F24" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D24)),ISNUMBER(SEARCH("Core Design",D24)),ISNUMBER(SEARCH("Mobile Terminology",D24)),ISNUMBER(SEARCH("Mobile Design",D24)),ISNUMBER(SEARCH("Mobile Integration",D24)),ISNUMBER(SEARCH("Testing Layer",D24)),ISNUMBER(SEARCH("Testing Offshore",D24)),ISNUMBER(SEARCH("Carrier",D24)),ISNUMBER(SEARCH("Barrier",D24))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="0" t="str">
+      <c r="E25" s="1" t="str">
         <f aca="false">E18</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F25" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D25)))&gt;0,"Billing PO","")</f>
+      <c r="F25" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D25)),ISNUMBER(SEARCH("Core Design",D25)),ISNUMBER(SEARCH("Mobile Terminology",D25)),ISNUMBER(SEARCH("Mobile Design",D25)),ISNUMBER(SEARCH("Mobile Integration",D25)),ISNUMBER(SEARCH("Testing Layer",D25)),ISNUMBER(SEARCH("Testing Offshore",D25)),ISNUMBER(SEARCH("Carrier",D25)),ISNUMBER(SEARCH("Barrier",D25))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="0" t="str">
+      <c r="E26" s="1" t="str">
         <f aca="false">E19</f>
         <v> SNMP</v>
       </c>
-      <c r="F26" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D26)))&gt;0,"Billing PO","")</f>
+      <c r="F26" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D26)),ISNUMBER(SEARCH("Core Design",D26)),ISNUMBER(SEARCH("Mobile Terminology",D26)),ISNUMBER(SEARCH("Mobile Design",D26)),ISNUMBER(SEARCH("Mobile Integration",D26)),ISNUMBER(SEARCH("Testing Layer",D26)),ISNUMBER(SEARCH("Testing Offshore",D26)),ISNUMBER(SEARCH("Carrier",D26)),ISNUMBER(SEARCH("Barrier",D26))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="0" t="str">
+      <c r="E27" s="1" t="str">
         <f aca="false">E20</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F27" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D27)))&gt;0,"Billing PO","")</f>
+      <c r="F27" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D27)),ISNUMBER(SEARCH("Core Design",D27)),ISNUMBER(SEARCH("Mobile Terminology",D27)),ISNUMBER(SEARCH("Mobile Design",D27)),ISNUMBER(SEARCH("Mobile Integration",D27)),ISNUMBER(SEARCH("Testing Layer",D27)),ISNUMBER(SEARCH("Testing Offshore",D27)),ISNUMBER(SEARCH("Carrier",D27)),ISNUMBER(SEARCH("Barrier",D27))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="11" t="s">
+      <c r="B28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E28" s="0" t="str">
+      <c r="E28" s="1" t="str">
         <f aca="false">E21</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F28" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D28)))&gt;0,"Billing PO","")</f>
+      <c r="F28" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D28)),ISNUMBER(SEARCH("Core Design",D28)),ISNUMBER(SEARCH("Mobile Terminology",D28)),ISNUMBER(SEARCH("Mobile Design",D28)),ISNUMBER(SEARCH("Mobile Integration",D28)),ISNUMBER(SEARCH("Testing Layer",D28)),ISNUMBER(SEARCH("Testing Offshore",D28)),ISNUMBER(SEARCH("Carrier",D28)),ISNUMBER(SEARCH("Barrier",D28))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="0" t="str">
+      <c r="E29" s="1" t="str">
         <f aca="false">E22</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F29" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D29)))&gt;0,"Billing PO","")</f>
+      <c r="F29" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D29)),ISNUMBER(SEARCH("Core Design",D29)),ISNUMBER(SEARCH("Mobile Terminology",D29)),ISNUMBER(SEARCH("Mobile Design",D29)),ISNUMBER(SEARCH("Mobile Integration",D29)),ISNUMBER(SEARCH("Testing Layer",D29)),ISNUMBER(SEARCH("Testing Offshore",D29)),ISNUMBER(SEARCH("Carrier",D29)),ISNUMBER(SEARCH("Barrier",D29))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="B30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="0" t="str">
+      <c r="E30" s="1" t="str">
         <f aca="false">E23</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F30" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D30)))&gt;0,"Billing PO","")</f>
+      <c r="F30" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D30)),ISNUMBER(SEARCH("Core Design",D30)),ISNUMBER(SEARCH("Mobile Terminology",D30)),ISNUMBER(SEARCH("Mobile Design",D30)),ISNUMBER(SEARCH("Mobile Integration",D30)),ISNUMBER(SEARCH("Testing Layer",D30)),ISNUMBER(SEARCH("Testing Offshore",D30)),ISNUMBER(SEARCH("Carrier",D30)),ISNUMBER(SEARCH("Barrier",D30))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="0" t="str">
+      <c r="E31" s="1" t="str">
         <f aca="false">E24</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F31" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D31)))&gt;0,"Billing PO","")</f>
+      <c r="F31" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D31)),ISNUMBER(SEARCH("Core Design",D31)),ISNUMBER(SEARCH("Mobile Terminology",D31)),ISNUMBER(SEARCH("Mobile Design",D31)),ISNUMBER(SEARCH("Mobile Integration",D31)),ISNUMBER(SEARCH("Testing Layer",D31)),ISNUMBER(SEARCH("Testing Offshore",D31)),ISNUMBER(SEARCH("Carrier",D31)),ISNUMBER(SEARCH("Barrier",D31))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="B32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E32" s="0" t="str">
+      <c r="E32" s="1" t="str">
         <f aca="false">E25</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F32" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D32)))&gt;0,"Billing PO","")</f>
+      <c r="F32" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D32)),ISNUMBER(SEARCH("Core Design",D32)),ISNUMBER(SEARCH("Mobile Terminology",D32)),ISNUMBER(SEARCH("Mobile Design",D32)),ISNUMBER(SEARCH("Mobile Integration",D32)),ISNUMBER(SEARCH("Testing Layer",D32)),ISNUMBER(SEARCH("Testing Offshore",D32)),ISNUMBER(SEARCH("Carrier",D32)),ISNUMBER(SEARCH("Barrier",D32))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="0" t="str">
+      <c r="E33" s="1" t="str">
         <f aca="false">E26</f>
         <v> SNMP</v>
       </c>
-      <c r="F33" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D33)))&gt;0,"Billing PO","")</f>
+      <c r="F33" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D33)),ISNUMBER(SEARCH("Core Design",D33)),ISNUMBER(SEARCH("Mobile Terminology",D33)),ISNUMBER(SEARCH("Mobile Design",D33)),ISNUMBER(SEARCH("Mobile Integration",D33)),ISNUMBER(SEARCH("Testing Layer",D33)),ISNUMBER(SEARCH("Testing Offshore",D33)),ISNUMBER(SEARCH("Carrier",D33)),ISNUMBER(SEARCH("Barrier",D33))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="0" t="s">
+      <c r="B34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="0" t="str">
+      <c r="E34" s="1" t="str">
         <f aca="false">E27</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F34" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D34)))&gt;0,"Billing PO","")</f>
+      <c r="F34" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D34)),ISNUMBER(SEARCH("Core Design",D34)),ISNUMBER(SEARCH("Mobile Terminology",D34)),ISNUMBER(SEARCH("Mobile Design",D34)),ISNUMBER(SEARCH("Mobile Integration",D34)),ISNUMBER(SEARCH("Testing Layer",D34)),ISNUMBER(SEARCH("Testing Offshore",D34)),ISNUMBER(SEARCH("Carrier",D34)),ISNUMBER(SEARCH("Barrier",D34))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="0" t="str">
+      <c r="E35" s="1" t="str">
         <f aca="false">E28</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F35" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D35)))&gt;0,"Billing PO","")</f>
+      <c r="F35" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D35)),ISNUMBER(SEARCH("Core Design",D35)),ISNUMBER(SEARCH("Mobile Terminology",D35)),ISNUMBER(SEARCH("Mobile Design",D35)),ISNUMBER(SEARCH("Mobile Integration",D35)),ISNUMBER(SEARCH("Testing Layer",D35)),ISNUMBER(SEARCH("Testing Offshore",D35)),ISNUMBER(SEARCH("Carrier",D35)),ISNUMBER(SEARCH("Barrier",D35))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="0" t="s">
+      <c r="B36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="0" t="str">
+      <c r="E36" s="1" t="str">
         <f aca="false">E29</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F36" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D36)))&gt;0,"Billing PO","")</f>
+      <c r="F36" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D36)),ISNUMBER(SEARCH("Core Design",D36)),ISNUMBER(SEARCH("Mobile Terminology",D36)),ISNUMBER(SEARCH("Mobile Design",D36)),ISNUMBER(SEARCH("Mobile Integration",D36)),ISNUMBER(SEARCH("Testing Layer",D36)),ISNUMBER(SEARCH("Testing Offshore",D36)),ISNUMBER(SEARCH("Carrier",D36)),ISNUMBER(SEARCH("Barrier",D36))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="0" t="str">
+      <c r="E37" s="1" t="str">
         <f aca="false">E30</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F37" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D37)))&gt;0,"Billing PO","")</f>
+      <c r="F37" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D37)),ISNUMBER(SEARCH("Core Design",D37)),ISNUMBER(SEARCH("Mobile Terminology",D37)),ISNUMBER(SEARCH("Mobile Design",D37)),ISNUMBER(SEARCH("Mobile Integration",D37)),ISNUMBER(SEARCH("Testing Layer",D37)),ISNUMBER(SEARCH("Testing Offshore",D37)),ISNUMBER(SEARCH("Carrier",D37)),ISNUMBER(SEARCH("Barrier",D37))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="0" t="s">
+      <c r="B38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="0" t="str">
+      <c r="E38" s="1" t="str">
         <f aca="false">E31</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F38" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D38)))&gt;0,"Billing PO","")</f>
+      <c r="F38" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D38)),ISNUMBER(SEARCH("Core Design",D38)),ISNUMBER(SEARCH("Mobile Terminology",D38)),ISNUMBER(SEARCH("Mobile Design",D38)),ISNUMBER(SEARCH("Mobile Integration",D38)),ISNUMBER(SEARCH("Testing Layer",D38)),ISNUMBER(SEARCH("Testing Offshore",D38)),ISNUMBER(SEARCH("Carrier",D38)),ISNUMBER(SEARCH("Barrier",D38))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E39" s="0" t="str">
+      <c r="E39" s="1" t="str">
         <f aca="false">E32</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F39" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D39)))&gt;0,"Billing PO","")</f>
+      <c r="F39" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D39)),ISNUMBER(SEARCH("Core Design",D39)),ISNUMBER(SEARCH("Mobile Terminology",D39)),ISNUMBER(SEARCH("Mobile Design",D39)),ISNUMBER(SEARCH("Mobile Integration",D39)),ISNUMBER(SEARCH("Testing Layer",D39)),ISNUMBER(SEARCH("Testing Offshore",D39)),ISNUMBER(SEARCH("Carrier",D39)),ISNUMBER(SEARCH("Barrier",D39))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="0" t="s">
+      <c r="B40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="0" t="str">
+      <c r="E40" s="1" t="str">
         <f aca="false">E33</f>
         <v> SNMP</v>
       </c>
-      <c r="F40" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D40)))&gt;0,"Billing PO","")</f>
+      <c r="F40" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D40)),ISNUMBER(SEARCH("Core Design",D40)),ISNUMBER(SEARCH("Mobile Terminology",D40)),ISNUMBER(SEARCH("Mobile Design",D40)),ISNUMBER(SEARCH("Mobile Integration",D40)),ISNUMBER(SEARCH("Testing Layer",D40)),ISNUMBER(SEARCH("Testing Offshore",D40)),ISNUMBER(SEARCH("Carrier",D40)),ISNUMBER(SEARCH("Barrier",D40))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E41" s="0" t="str">
+      <c r="E41" s="1" t="str">
         <f aca="false">E34</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F41" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D41)))&gt;0,"Billing PO","")</f>
+      <c r="F41" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D41)),ISNUMBER(SEARCH("Core Design",D41)),ISNUMBER(SEARCH("Mobile Terminology",D41)),ISNUMBER(SEARCH("Mobile Design",D41)),ISNUMBER(SEARCH("Mobile Integration",D41)),ISNUMBER(SEARCH("Testing Layer",D41)),ISNUMBER(SEARCH("Testing Offshore",D41)),ISNUMBER(SEARCH("Carrier",D41)),ISNUMBER(SEARCH("Barrier",D41))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="0" t="s">
+      <c r="B42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="0" t="str">
+      <c r="E42" s="1" t="str">
         <f aca="false">E35</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F42" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D42)))&gt;0,"Billing PO","")</f>
+      <c r="F42" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D42)),ISNUMBER(SEARCH("Core Design",D42)),ISNUMBER(SEARCH("Mobile Terminology",D42)),ISNUMBER(SEARCH("Mobile Design",D42)),ISNUMBER(SEARCH("Mobile Integration",D42)),ISNUMBER(SEARCH("Testing Layer",D42)),ISNUMBER(SEARCH("Testing Offshore",D42)),ISNUMBER(SEARCH("Carrier",D42)),ISNUMBER(SEARCH("Barrier",D42))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E43" s="0" t="str">
+      <c r="E43" s="1" t="str">
         <f aca="false">E36</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F43" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D43)))&gt;0,"Billing PO","")</f>
+      <c r="F43" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D43)),ISNUMBER(SEARCH("Core Design",D43)),ISNUMBER(SEARCH("Mobile Terminology",D43)),ISNUMBER(SEARCH("Mobile Design",D43)),ISNUMBER(SEARCH("Mobile Integration",D43)),ISNUMBER(SEARCH("Testing Layer",D43)),ISNUMBER(SEARCH("Testing Offshore",D43)),ISNUMBER(SEARCH("Carrier",D43)),ISNUMBER(SEARCH("Barrier",D43))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="0" t="s">
+      <c r="B44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E44" s="0" t="str">
+      <c r="E44" s="1" t="str">
         <f aca="false">E37</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F44" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D44)))&gt;0,"Billing PO","")</f>
+      <c r="F44" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D44)),ISNUMBER(SEARCH("Core Design",D44)),ISNUMBER(SEARCH("Mobile Terminology",D44)),ISNUMBER(SEARCH("Mobile Design",D44)),ISNUMBER(SEARCH("Mobile Integration",D44)),ISNUMBER(SEARCH("Testing Layer",D44)),ISNUMBER(SEARCH("Testing Offshore",D44)),ISNUMBER(SEARCH("Carrier",D44)),ISNUMBER(SEARCH("Barrier",D44))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E45" s="0" t="str">
+      <c r="E45" s="1" t="str">
         <f aca="false">E38</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F45" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D45)))&gt;0,"Billing PO","")</f>
+      <c r="F45" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D45)),ISNUMBER(SEARCH("Core Design",D45)),ISNUMBER(SEARCH("Mobile Terminology",D45)),ISNUMBER(SEARCH("Mobile Design",D45)),ISNUMBER(SEARCH("Mobile Integration",D45)),ISNUMBER(SEARCH("Testing Layer",D45)),ISNUMBER(SEARCH("Testing Offshore",D45)),ISNUMBER(SEARCH("Carrier",D45)),ISNUMBER(SEARCH("Barrier",D45))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="0" t="s">
+      <c r="B46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="0" t="str">
+      <c r="E46" s="1" t="str">
         <f aca="false">E39</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F46" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D46)))&gt;0,"Billing PO","")</f>
+      <c r="F46" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D46)),ISNUMBER(SEARCH("Core Design",D46)),ISNUMBER(SEARCH("Mobile Terminology",D46)),ISNUMBER(SEARCH("Mobile Design",D46)),ISNUMBER(SEARCH("Mobile Integration",D46)),ISNUMBER(SEARCH("Testing Layer",D46)),ISNUMBER(SEARCH("Testing Offshore",D46)),ISNUMBER(SEARCH("Carrier",D46)),ISNUMBER(SEARCH("Barrier",D46))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E47" s="0" t="str">
+      <c r="E47" s="1" t="str">
         <f aca="false">E40</f>
         <v> SNMP</v>
       </c>
-      <c r="F47" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D47)))&gt;0,"Billing PO","")</f>
+      <c r="F47" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D47)),ISNUMBER(SEARCH("Core Design",D47)),ISNUMBER(SEARCH("Mobile Terminology",D47)),ISNUMBER(SEARCH("Mobile Design",D47)),ISNUMBER(SEARCH("Mobile Integration",D47)),ISNUMBER(SEARCH("Testing Layer",D47)),ISNUMBER(SEARCH("Testing Offshore",D47)),ISNUMBER(SEARCH("Carrier",D47)),ISNUMBER(SEARCH("Barrier",D47))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="11" t="s">
+      <c r="B48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E48" s="0" t="str">
+      <c r="E48" s="1" t="str">
         <f aca="false">E41</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F48" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D48)))&gt;0,"Billing PO","")</f>
+      <c r="F48" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D48)),ISNUMBER(SEARCH("Core Design",D48)),ISNUMBER(SEARCH("Mobile Terminology",D48)),ISNUMBER(SEARCH("Mobile Design",D48)),ISNUMBER(SEARCH("Mobile Integration",D48)),ISNUMBER(SEARCH("Testing Layer",D48)),ISNUMBER(SEARCH("Testing Offshore",D48)),ISNUMBER(SEARCH("Carrier",D48)),ISNUMBER(SEARCH("Barrier",D48))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E49" s="0" t="str">
+      <c r="E49" s="1" t="str">
         <f aca="false">E42</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F49" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D49)))&gt;0,"Billing PO","")</f>
+      <c r="F49" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D49)),ISNUMBER(SEARCH("Core Design",D49)),ISNUMBER(SEARCH("Mobile Terminology",D49)),ISNUMBER(SEARCH("Mobile Design",D49)),ISNUMBER(SEARCH("Mobile Integration",D49)),ISNUMBER(SEARCH("Testing Layer",D49)),ISNUMBER(SEARCH("Testing Offshore",D49)),ISNUMBER(SEARCH("Carrier",D49)),ISNUMBER(SEARCH("Barrier",D49))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="0" t="s">
+      <c r="B50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E50" s="0" t="str">
+      <c r="E50" s="1" t="str">
         <f aca="false">E43</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F50" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D50)))&gt;0,"Billing PO","")</f>
+      <c r="F50" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D50)),ISNUMBER(SEARCH("Core Design",D50)),ISNUMBER(SEARCH("Mobile Terminology",D50)),ISNUMBER(SEARCH("Mobile Design",D50)),ISNUMBER(SEARCH("Mobile Integration",D50)),ISNUMBER(SEARCH("Testing Layer",D50)),ISNUMBER(SEARCH("Testing Offshore",D50)),ISNUMBER(SEARCH("Carrier",D50)),ISNUMBER(SEARCH("Barrier",D50))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E51" s="0" t="str">
+      <c r="E51" s="1" t="str">
         <f aca="false">E44</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F51" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D51)))&gt;0,"Billing PO","")</f>
+      <c r="F51" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D51)),ISNUMBER(SEARCH("Core Design",D51)),ISNUMBER(SEARCH("Mobile Terminology",D51)),ISNUMBER(SEARCH("Mobile Design",D51)),ISNUMBER(SEARCH("Mobile Integration",D51)),ISNUMBER(SEARCH("Testing Layer",D51)),ISNUMBER(SEARCH("Testing Offshore",D51)),ISNUMBER(SEARCH("Carrier",D51)),ISNUMBER(SEARCH("Barrier",D51))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="11" t="s">
+      <c r="B52" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E52" s="0" t="str">
+      <c r="E52" s="1" t="str">
         <f aca="false">E45</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F52" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D52)))&gt;0,"Billing PO","")</f>
+      <c r="F52" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D52)),ISNUMBER(SEARCH("Core Design",D52)),ISNUMBER(SEARCH("Mobile Terminology",D52)),ISNUMBER(SEARCH("Mobile Design",D52)),ISNUMBER(SEARCH("Mobile Integration",D52)),ISNUMBER(SEARCH("Testing Layer",D52)),ISNUMBER(SEARCH("Testing Offshore",D52)),ISNUMBER(SEARCH("Carrier",D52)),ISNUMBER(SEARCH("Barrier",D52))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="0" t="str">
+      <c r="E53" s="1" t="str">
         <f aca="false">E46</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F53" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D53)))&gt;0,"Billing PO","")</f>
+      <c r="F53" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D53)),ISNUMBER(SEARCH("Core Design",D53)),ISNUMBER(SEARCH("Mobile Terminology",D53)),ISNUMBER(SEARCH("Mobile Design",D53)),ISNUMBER(SEARCH("Mobile Integration",D53)),ISNUMBER(SEARCH("Testing Layer",D53)),ISNUMBER(SEARCH("Testing Offshore",D53)),ISNUMBER(SEARCH("Carrier",D53)),ISNUMBER(SEARCH("Barrier",D53))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="11" t="s">
+      <c r="B54" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E54" s="0" t="str">
+      <c r="E54" s="1" t="str">
         <f aca="false">E47</f>
         <v> SNMP</v>
       </c>
-      <c r="F54" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D54)))&gt;0,"Billing PO","")</f>
+      <c r="F54" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D54)),ISNUMBER(SEARCH("Core Design",D54)),ISNUMBER(SEARCH("Mobile Terminology",D54)),ISNUMBER(SEARCH("Mobile Design",D54)),ISNUMBER(SEARCH("Mobile Integration",D54)),ISNUMBER(SEARCH("Testing Layer",D54)),ISNUMBER(SEARCH("Testing Offshore",D54)),ISNUMBER(SEARCH("Carrier",D54)),ISNUMBER(SEARCH("Barrier",D54))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E55" s="0" t="str">
+      <c r="E55" s="1" t="str">
         <f aca="false">E48</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F55" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D55)))&gt;0,"Billing PO","")</f>
+      <c r="F55" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D55)),ISNUMBER(SEARCH("Core Design",D55)),ISNUMBER(SEARCH("Mobile Terminology",D55)),ISNUMBER(SEARCH("Mobile Design",D55)),ISNUMBER(SEARCH("Mobile Integration",D55)),ISNUMBER(SEARCH("Testing Layer",D55)),ISNUMBER(SEARCH("Testing Offshore",D55)),ISNUMBER(SEARCH("Carrier",D55)),ISNUMBER(SEARCH("Barrier",D55))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="11" t="s">
+      <c r="B56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="0" t="str">
+      <c r="E56" s="1" t="str">
         <f aca="false">E49</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F56" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D56)))&gt;0,"Billing PO","")</f>
+      <c r="F56" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D56)),ISNUMBER(SEARCH("Core Design",D56)),ISNUMBER(SEARCH("Mobile Terminology",D56)),ISNUMBER(SEARCH("Mobile Design",D56)),ISNUMBER(SEARCH("Mobile Integration",D56)),ISNUMBER(SEARCH("Testing Layer",D56)),ISNUMBER(SEARCH("Testing Offshore",D56)),ISNUMBER(SEARCH("Carrier",D56)),ISNUMBER(SEARCH("Barrier",D56))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E57" s="0" t="str">
+      <c r="E57" s="1" t="str">
         <f aca="false">E50</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F57" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D57)))&gt;0,"Billing PO","")</f>
+      <c r="F57" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D57)),ISNUMBER(SEARCH("Core Design",D57)),ISNUMBER(SEARCH("Mobile Terminology",D57)),ISNUMBER(SEARCH("Mobile Design",D57)),ISNUMBER(SEARCH("Mobile Integration",D57)),ISNUMBER(SEARCH("Testing Layer",D57)),ISNUMBER(SEARCH("Testing Offshore",D57)),ISNUMBER(SEARCH("Carrier",D57)),ISNUMBER(SEARCH("Barrier",D57))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="0" t="s">
+      <c r="B58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="0" t="str">
+      <c r="E58" s="1" t="str">
         <f aca="false">E51</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F58" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D58)))&gt;0,"Billing PO","")</f>
+      <c r="F58" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D58)),ISNUMBER(SEARCH("Core Design",D58)),ISNUMBER(SEARCH("Mobile Terminology",D58)),ISNUMBER(SEARCH("Mobile Design",D58)),ISNUMBER(SEARCH("Mobile Integration",D58)),ISNUMBER(SEARCH("Testing Layer",D58)),ISNUMBER(SEARCH("Testing Offshore",D58)),ISNUMBER(SEARCH("Carrier",D58)),ISNUMBER(SEARCH("Barrier",D58))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="0" t="str">
+      <c r="E59" s="1" t="str">
         <f aca="false">E52</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F59" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D59)))&gt;0,"Billing PO","")</f>
+      <c r="F59" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D59)),ISNUMBER(SEARCH("Core Design",D59)),ISNUMBER(SEARCH("Mobile Terminology",D59)),ISNUMBER(SEARCH("Mobile Design",D59)),ISNUMBER(SEARCH("Mobile Integration",D59)),ISNUMBER(SEARCH("Testing Layer",D59)),ISNUMBER(SEARCH("Testing Offshore",D59)),ISNUMBER(SEARCH("Carrier",D59)),ISNUMBER(SEARCH("Barrier",D59))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="0" t="s">
+      <c r="B60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E60" s="0" t="str">
+      <c r="E60" s="1" t="str">
         <f aca="false">E53</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F60" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D60)))&gt;0,"Billing PO","")</f>
+      <c r="F60" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D60)),ISNUMBER(SEARCH("Core Design",D60)),ISNUMBER(SEARCH("Mobile Terminology",D60)),ISNUMBER(SEARCH("Mobile Design",D60)),ISNUMBER(SEARCH("Mobile Integration",D60)),ISNUMBER(SEARCH("Testing Layer",D60)),ISNUMBER(SEARCH("Testing Offshore",D60)),ISNUMBER(SEARCH("Carrier",D60)),ISNUMBER(SEARCH("Barrier",D60))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E61" s="0" t="str">
+      <c r="E61" s="1" t="str">
         <f aca="false">E54</f>
         <v> SNMP</v>
       </c>
-      <c r="F61" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D61)))&gt;0,"Billing PO","")</f>
+      <c r="F61" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D61)),ISNUMBER(SEARCH("Core Design",D61)),ISNUMBER(SEARCH("Mobile Terminology",D61)),ISNUMBER(SEARCH("Mobile Design",D61)),ISNUMBER(SEARCH("Mobile Integration",D61)),ISNUMBER(SEARCH("Testing Layer",D61)),ISNUMBER(SEARCH("Testing Offshore",D61)),ISNUMBER(SEARCH("Carrier",D61)),ISNUMBER(SEARCH("Barrier",D61))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D62" s="0" t="s">
+      <c r="B62" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E62" s="0" t="str">
+      <c r="E62" s="1" t="str">
         <f aca="false">E55</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F62" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D62)))&gt;0,"Billing PO","")</f>
+      <c r="F62" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D62)),ISNUMBER(SEARCH("Core Design",D62)),ISNUMBER(SEARCH("Mobile Terminology",D62)),ISNUMBER(SEARCH("Mobile Design",D62)),ISNUMBER(SEARCH("Mobile Integration",D62)),ISNUMBER(SEARCH("Testing Layer",D62)),ISNUMBER(SEARCH("Testing Offshore",D62)),ISNUMBER(SEARCH("Carrier",D62)),ISNUMBER(SEARCH("Barrier",D62))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E63" s="0" t="str">
+      <c r="E63" s="1" t="str">
         <f aca="false">E56</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F63" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D63)))&gt;0,"Billing PO","")</f>
+      <c r="F63" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D63)),ISNUMBER(SEARCH("Core Design",D63)),ISNUMBER(SEARCH("Mobile Terminology",D63)),ISNUMBER(SEARCH("Mobile Design",D63)),ISNUMBER(SEARCH("Mobile Integration",D63)),ISNUMBER(SEARCH("Testing Layer",D63)),ISNUMBER(SEARCH("Testing Offshore",D63)),ISNUMBER(SEARCH("Carrier",D63)),ISNUMBER(SEARCH("Barrier",D63))),"Billing PO","")</f>
         <v>Billing PO</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="0" t="s">
+      <c r="B64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E64" s="0" t="str">
+      <c r="E64" s="1" t="str">
         <f aca="false">E57</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F64" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D64)))&gt;0,"Billing PO","")</f>
+      <c r="F64" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D64)),ISNUMBER(SEARCH("Core Design",D64)),ISNUMBER(SEARCH("Mobile Terminology",D64)),ISNUMBER(SEARCH("Mobile Design",D64)),ISNUMBER(SEARCH("Mobile Integration",D64)),ISNUMBER(SEARCH("Testing Layer",D64)),ISNUMBER(SEARCH("Testing Offshore",D64)),ISNUMBER(SEARCH("Carrier",D64)),ISNUMBER(SEARCH("Barrier",D64))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E65" s="0" t="str">
+      <c r="E65" s="1" t="str">
         <f aca="false">E58</f>
         <v> VoIP, IMS, MPLS, ISDN, PSTN</v>
       </c>
-      <c r="F65" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D65)))&gt;0,"Billing PO","")</f>
+      <c r="F65" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D65)),ISNUMBER(SEARCH("Core Design",D65)),ISNUMBER(SEARCH("Mobile Terminology",D65)),ISNUMBER(SEARCH("Mobile Design",D65)),ISNUMBER(SEARCH("Mobile Integration",D65)),ISNUMBER(SEARCH("Testing Layer",D65)),ISNUMBER(SEARCH("Testing Offshore",D65)),ISNUMBER(SEARCH("Carrier",D65)),ISNUMBER(SEARCH("Barrier",D65))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="0" t="s">
+      <c r="B66" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E66" s="0" t="str">
+      <c r="E66" s="1" t="str">
         <f aca="false">E59</f>
         <v> SIP, ISDN, Codecs, H.323</v>
       </c>
-      <c r="F66" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D66)))&gt;0,"Billing PO","")</f>
+      <c r="F66" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D66)),ISNUMBER(SEARCH("Core Design",D66)),ISNUMBER(SEARCH("Mobile Terminology",D66)),ISNUMBER(SEARCH("Mobile Design",D66)),ISNUMBER(SEARCH("Mobile Integration",D66)),ISNUMBER(SEARCH("Testing Layer",D66)),ISNUMBER(SEARCH("Testing Offshore",D66)),ISNUMBER(SEARCH("Carrier",D66)),ISNUMBER(SEARCH("Barrier",D66))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E67" s="0" t="str">
+      <c r="E67" s="1" t="str">
         <f aca="false">E60</f>
         <v> GPRS, CDMA, GSM, UMTS</v>
       </c>
-      <c r="F67" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D67)))&gt;0,"Billing PO","")</f>
+      <c r="F67" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D67)),ISNUMBER(SEARCH("Core Design",D67)),ISNUMBER(SEARCH("Mobile Terminology",D67)),ISNUMBER(SEARCH("Mobile Design",D67)),ISNUMBER(SEARCH("Mobile Integration",D67)),ISNUMBER(SEARCH("Testing Layer",D67)),ISNUMBER(SEARCH("Testing Offshore",D67)),ISNUMBER(SEARCH("Carrier",D67)),ISNUMBER(SEARCH("Barrier",D67))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" s="0" t="s">
+      <c r="B68" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E68" s="0" t="str">
+      <c r="E68" s="1" t="str">
         <f aca="false">E61</f>
         <v> SNMP</v>
       </c>
-      <c r="F68" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D68)))&gt;0,"Billing PO","")</f>
+      <c r="F68" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D68)),ISNUMBER(SEARCH("Core Design",D68)),ISNUMBER(SEARCH("Mobile Terminology",D68)),ISNUMBER(SEARCH("Mobile Design",D68)),ISNUMBER(SEARCH("Mobile Integration",D68)),ISNUMBER(SEARCH("Testing Layer",D68)),ISNUMBER(SEARCH("Testing Offshore",D68)),ISNUMBER(SEARCH("Carrier",D68)),ISNUMBER(SEARCH("Barrier",D68))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E69" s="0" t="str">
+      <c r="E69" s="1" t="str">
         <f aca="false">E62</f>
         <v> ARP, STP, L2TP, PPP</v>
       </c>
-      <c r="F69" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D69)))&gt;0,"Billing PO","")</f>
+      <c r="F69" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D69)),ISNUMBER(SEARCH("Core Design",D69)),ISNUMBER(SEARCH("Mobile Terminology",D69)),ISNUMBER(SEARCH("Mobile Design",D69)),ISNUMBER(SEARCH("Mobile Integration",D69)),ISNUMBER(SEARCH("Testing Layer",D69)),ISNUMBER(SEARCH("Testing Offshore",D69)),ISNUMBER(SEARCH("Carrier",D69)),ISNUMBER(SEARCH("Barrier",D69))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="0" t="s">
+      <c r="B70" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E70" s="0" t="str">
+      <c r="E70" s="1" t="str">
         <f aca="false">E63</f>
         <v> ICMP, BGP, ISIS, MPLS</v>
       </c>
-      <c r="F70" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D70)))&gt;0,"Billing PO","")</f>
+      <c r="F70" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D70)),ISNUMBER(SEARCH("Core Design",D70)),ISNUMBER(SEARCH("Mobile Terminology",D70)),ISNUMBER(SEARCH("Mobile Design",D70)),ISNUMBER(SEARCH("Mobile Integration",D70)),ISNUMBER(SEARCH("Testing Layer",D70)),ISNUMBER(SEARCH("Testing Offshore",D70)),ISNUMBER(SEARCH("Carrier",D70)),ISNUMBER(SEARCH("Barrier",D70))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E71" s="0" t="str">
+      <c r="E71" s="1" t="str">
         <f aca="false">E64</f>
         <v> ATM, TCP/IP, LAN/VLAN, SSH</v>
       </c>
-      <c r="F71" s="0" t="str">
-        <f aca="false">IF(SUMPRODUCT(--ISNUMBER(SEARCH({"Core Activation","Core Design","Mobile Terminology","Mobile Design","Mobile Integration","Testing Layer","Testing Offshore","Carrier","Barrier"},D71)))&gt;0,"Billing PO","")</f>
+      <c r="F71" s="1" t="str">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Core Activation",D71)),ISNUMBER(SEARCH("Core Design",D71)),ISNUMBER(SEARCH("Mobile Terminology",D71)),ISNUMBER(SEARCH("Mobile Design",D71)),ISNUMBER(SEARCH("Mobile Integration",D71)),ISNUMBER(SEARCH("Testing Layer",D71)),ISNUMBER(SEARCH("Testing Offshore",D71)),ISNUMBER(SEARCH("Carrier",D71)),ISNUMBER(SEARCH("Barrier",D71))),"Billing PO","")</f>
         <v/>
       </c>
     </row>
